--- a/cv.xlsx
+++ b/cv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orion/Library/Containers/com.panic.transmit.mas/Data/Library/Caches/Transmit/3409C16A-DD89-49BA-ABC4-37FAF2E1FCF0/10.122.14.119/home/pzhou/git/cv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orion/Library/Containers/com.panic.transmit.mas/Data/Library/Caches/Transmit/AA945275-8638-4459-9D4E-8AB1D677FC6B/10.122.14.119/home/pzhou/git/cv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D41BAA-C532-FA4F-BF07-68AA62031079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6F3126-6986-0547-A02A-4114BF76B16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17400" yWindow="9200" windowWidth="22540" windowHeight="15180" xr2:uid="{49BEF855-14FC-304C-9B93-8FA563204E38}"/>
+    <workbookView xWindow="21420" yWindow="10160" windowWidth="22540" windowHeight="15180" xr2:uid="{49BEF855-14FC-304C-9B93-8FA563204E38}"/>
   </bookViews>
   <sheets>
     <sheet name="positions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="196">
   <si>
     <t>loc</t>
   </si>
@@ -364,9 +364,6 @@
     <t>__*Plant Journal*__. 2019, 100: 1052-1065.</t>
   </si>
   <si>
-    <t>__*Molecular Plant*__. 2019, 12: 410-425.</t>
-  </si>
-  <si>
     <t>Anderson SN, **Zhou P**, Higgins K, Brandvain Y, Springer NM</t>
   </si>
   <si>
@@ -613,12 +610,6 @@
     <t>Guan J, Wang Z, Liu S, Kong X, Wang F, Sun G, Geng S, Mao L^\*^, **Zhou P^\*^**,  Li A^\*^</t>
   </si>
   <si>
-    <t>__*Plant Commun*__. 2024, 5: 100977.</t>
-  </si>
-  <si>
-    <t>__*Plant Cell*__. 2022, 34: 514-534.</t>
-  </si>
-  <si>
     <t>__*Proc Natl Acad Sci U S A.*__. 2021. 118 (47) e2109332118.</t>
   </si>
   <si>
@@ -674,13 +665,25 @@
   </si>
   <si>
     <t>Young ND, Debellé F, Oldroyd GED, …, **Zhou P**, …, et al</t>
+  </si>
+  <si>
+    <t>[A near Telomere‐to‐telomere Genome Assembly and Graph‐based Pangenome of Tartary Buckwheat (Fagopyrum Tataricum)](https://doi.org/10.1111/pbi.70333)</t>
+  </si>
+  <si>
+    <t>Li W, Liang H, Sun J, Zhang X, He Q, **Zhou P^\#^**,  Huo D^\#^</t>
+  </si>
+  <si>
+    <t>__*Plant Biotechnol J*__. 2025:23(12):5797–5799.</t>
+  </si>
+  <si>
+    <t>__*Mol Plant*__. 2019, 12: 410-425.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -708,6 +711,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -729,9 +738,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1046,7 +1056,1576 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3854BA9-2B2F-4849-8499-B1FE2AB1C1F4}">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.33203125" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>2009</v>
+      </c>
+      <c r="G2">
+        <v>2015</v>
+      </c>
+      <c r="H2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>2007</v>
+      </c>
+      <c r="G3">
+        <v>2009</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>2003</v>
+      </c>
+      <c r="G4">
+        <v>2007</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5">
+        <v>2021</v>
+      </c>
+      <c r="G5">
+        <v>9999</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>2016</v>
+      </c>
+      <c r="G6">
+        <v>2021</v>
+      </c>
+      <c r="H6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>2015</v>
+      </c>
+      <c r="G7">
+        <v>2016</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>2011</v>
+      </c>
+      <c r="G8">
+        <v>2012</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>2025</v>
+      </c>
+      <c r="G9">
+        <v>2025</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>2024</v>
+      </c>
+      <c r="G10">
+        <v>2024</v>
+      </c>
+      <c r="H10" t="s">
+        <v>169</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>2022</v>
+      </c>
+      <c r="G11">
+        <v>2022</v>
+      </c>
+      <c r="H11" t="s">
+        <v>189</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>2020</v>
+      </c>
+      <c r="G12">
+        <v>2020</v>
+      </c>
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>2019</v>
+      </c>
+      <c r="G13">
+        <v>2019</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>2024</v>
+      </c>
+      <c r="G14">
+        <v>2024</v>
+      </c>
+      <c r="H14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>2024</v>
+      </c>
+      <c r="G15">
+        <v>2024</v>
+      </c>
+      <c r="H15" t="s">
+        <v>180</v>
+      </c>
+      <c r="I15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>2023</v>
+      </c>
+      <c r="G16">
+        <v>2023</v>
+      </c>
+      <c r="H16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>2022</v>
+      </c>
+      <c r="G17">
+        <v>2022</v>
+      </c>
+      <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>2021</v>
+      </c>
+      <c r="G18">
+        <v>2021</v>
+      </c>
+      <c r="H18" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>2021</v>
+      </c>
+      <c r="G19">
+        <v>2021</v>
+      </c>
+      <c r="H19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>2021</v>
+      </c>
+      <c r="G20">
+        <v>2021</v>
+      </c>
+      <c r="H20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>2021</v>
+      </c>
+      <c r="G21">
+        <v>2021</v>
+      </c>
+      <c r="H21" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>2021</v>
+      </c>
+      <c r="G22">
+        <v>2021</v>
+      </c>
+      <c r="H22" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>2020</v>
+      </c>
+      <c r="G23">
+        <v>2020</v>
+      </c>
+      <c r="H23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>2020</v>
+      </c>
+      <c r="G24">
+        <v>2020</v>
+      </c>
+      <c r="H24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>2019</v>
+      </c>
+      <c r="G25">
+        <v>2019</v>
+      </c>
+      <c r="H25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>2019</v>
+      </c>
+      <c r="G26">
+        <v>2019</v>
+      </c>
+      <c r="H26" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>2017</v>
+      </c>
+      <c r="G27">
+        <v>2017</v>
+      </c>
+      <c r="H27" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>2017</v>
+      </c>
+      <c r="G28">
+        <v>2017</v>
+      </c>
+      <c r="H28" t="s">
+        <v>119</v>
+      </c>
+      <c r="I28" t="s">
+        <v>10</v>
+      </c>
+      <c r="J28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>2017</v>
+      </c>
+      <c r="G29">
+        <v>2017</v>
+      </c>
+      <c r="H29" t="s">
+        <v>190</v>
+      </c>
+      <c r="I29" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>2017</v>
+      </c>
+      <c r="G30">
+        <v>2017</v>
+      </c>
+      <c r="H30" t="s">
+        <v>116</v>
+      </c>
+      <c r="I30" t="s">
+        <v>10</v>
+      </c>
+      <c r="J30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31">
+        <v>2016</v>
+      </c>
+      <c r="G31">
+        <v>2016</v>
+      </c>
+      <c r="H31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>2014</v>
+      </c>
+      <c r="G32">
+        <v>2014</v>
+      </c>
+      <c r="H32" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33">
+        <v>2013</v>
+      </c>
+      <c r="G33">
+        <v>2013</v>
+      </c>
+      <c r="H33" t="s">
+        <v>122</v>
+      </c>
+      <c r="I33" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>2013</v>
+      </c>
+      <c r="G34">
+        <v>2013</v>
+      </c>
+      <c r="H34" t="s">
+        <v>87</v>
+      </c>
+      <c r="I34" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35">
+        <v>2013</v>
+      </c>
+      <c r="G35">
+        <v>2013</v>
+      </c>
+      <c r="H35" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36">
+        <v>2012</v>
+      </c>
+      <c r="G36">
+        <v>2012</v>
+      </c>
+      <c r="H36" t="s">
+        <v>124</v>
+      </c>
+      <c r="I36" t="s">
+        <v>10</v>
+      </c>
+      <c r="J36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37">
+        <v>2011</v>
+      </c>
+      <c r="G37">
+        <v>2011</v>
+      </c>
+      <c r="H37" t="s">
+        <v>191</v>
+      </c>
+      <c r="I37" t="s">
+        <v>10</v>
+      </c>
+      <c r="J37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38">
+        <v>2020</v>
+      </c>
+      <c r="G38">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" t="s">
+        <v>47</v>
+      </c>
+      <c r="F39">
+        <v>2019</v>
+      </c>
+      <c r="G39">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40">
+        <v>2018</v>
+      </c>
+      <c r="G40">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41">
+        <v>2014</v>
+      </c>
+      <c r="G41">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42">
+        <v>2013</v>
+      </c>
+      <c r="G42">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43">
+        <v>2011</v>
+      </c>
+      <c r="G43">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44">
+        <v>2011</v>
+      </c>
+      <c r="G44">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45">
+        <v>2010</v>
+      </c>
+      <c r="G45">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46">
+        <v>2019</v>
+      </c>
+      <c r="G46">
+        <v>2019</v>
+      </c>
+      <c r="H46" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" t="s">
+        <v>10</v>
+      </c>
+      <c r="J46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47">
+        <v>2019</v>
+      </c>
+      <c r="G47">
+        <v>2019</v>
+      </c>
+      <c r="H47" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48">
+        <v>2016</v>
+      </c>
+      <c r="G48">
+        <v>2016</v>
+      </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" t="s">
+        <v>10</v>
+      </c>
+      <c r="J48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49">
+        <v>2016</v>
+      </c>
+      <c r="G49">
+        <v>2016</v>
+      </c>
+      <c r="H49" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" t="s">
+        <v>10</v>
+      </c>
+      <c r="J49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D4E204-A097-E246-8420-89EA1CD35275}">
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -1100,13 +2679,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>2009</v>
@@ -1115,13 +2694,10 @@
         <v>2015</v>
       </c>
       <c r="H2" t="s">
-        <v>187</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1132,13 +2708,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="F3">
         <v>2007</v>
@@ -1150,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="J3" t="s">
         <v>10</v>
@@ -1164,13 +2740,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="F4">
         <v>2003</v>
@@ -1196,13 +2772,13 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F5">
         <v>2021</v>
@@ -1228,13 +2804,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="F6">
         <v>2016</v>
@@ -1243,10 +2819,10 @@
         <v>2021</v>
       </c>
       <c r="H6" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
@@ -1260,13 +2836,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="F7">
         <v>2015</v>
@@ -1286,28 +2862,28 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="F8">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="G8">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
@@ -1318,28 +2894,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="G9">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="H9" t="s">
-        <v>170</v>
+        <v>33</v>
       </c>
       <c r="I9" t="s">
         <v>10</v>
@@ -1350,162 +2926,162 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="G10">
-        <v>2022</v>
-      </c>
-      <c r="H10" t="s">
-        <v>192</v>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="I10" t="s">
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G11">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G12">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="I12" t="s">
         <v>10</v>
       </c>
       <c r="J12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="G13">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="H13" t="s">
-        <v>193</v>
+        <v>64</v>
       </c>
       <c r="I13" t="s">
         <v>10</v>
       </c>
       <c r="J13" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D14" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="G14">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="H14" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
         <v>10</v>
       </c>
       <c r="J14" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1516,10 +3092,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -1531,7 +3107,7 @@
         <v>2024</v>
       </c>
       <c r="H15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I15" t="s">
         <v>10</v>
@@ -1548,22 +3124,22 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G16">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H16" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I16" t="s">
         <v>10</v>
@@ -1580,22 +3156,22 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G17">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H17" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I17" t="s">
         <v>10</v>
@@ -1612,22 +3188,22 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G18">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H18" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
         <v>10</v>
@@ -1644,10 +3220,10 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" t="s">
         <v>158</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -1659,7 +3235,7 @@
         <v>2021</v>
       </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="I19" t="s">
         <v>10</v>
@@ -1676,10 +3252,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -1691,7 +3267,7 @@
         <v>2021</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s">
         <v>10</v>
@@ -1708,10 +3284,10 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -1723,7 +3299,7 @@
         <v>2021</v>
       </c>
       <c r="H21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s">
         <v>10</v>
@@ -1740,10 +3316,10 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -1755,7 +3331,7 @@
         <v>2021</v>
       </c>
       <c r="H22" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I22" t="s">
         <v>10</v>
@@ -1772,22 +3348,22 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G23">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H23" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I23" t="s">
         <v>10</v>
@@ -1804,10 +3380,10 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -1819,7 +3395,7 @@
         <v>2020</v>
       </c>
       <c r="H24" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="I24" t="s">
         <v>10</v>
@@ -1836,22 +3412,22 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G25">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I25" t="s">
         <v>10</v>
@@ -1868,10 +3444,10 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -1883,7 +3459,7 @@
         <v>2019</v>
       </c>
       <c r="H26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I26" t="s">
         <v>10</v>
@@ -1900,22 +3476,22 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G27">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="H27" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I27" t="s">
         <v>10</v>
@@ -1932,10 +3508,10 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -1947,7 +3523,7 @@
         <v>2017</v>
       </c>
       <c r="H28" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="I28" t="s">
         <v>10</v>
@@ -1964,10 +3540,10 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -1979,7 +3555,7 @@
         <v>2017</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I29" t="s">
         <v>10</v>
@@ -1996,22 +3572,22 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G30">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s">
         <v>10</v>
@@ -2028,22 +3604,22 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="G31">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="H31" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="I31" t="s">
         <v>10</v>
@@ -2060,22 +3636,22 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="G32">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="H32" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s">
         <v>10</v>
@@ -2092,22 +3668,22 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G33">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H33" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="I33" t="s">
         <v>10</v>
@@ -2124,10 +3700,10 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -2139,7 +3715,7 @@
         <v>2013</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="I34" t="s">
         <v>10</v>
@@ -2156,22 +3732,22 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G35">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="I35" t="s">
         <v>10</v>
@@ -2188,22 +3764,22 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="G36">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H36" t="s">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="I36" t="s">
         <v>10</v>
@@ -2214,48 +3790,66 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F37">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="G37">
-        <v>2020</v>
+        <v>2012</v>
+      </c>
+      <c r="H37" t="s">
+        <v>124</v>
+      </c>
+      <c r="I37" t="s">
+        <v>10</v>
+      </c>
+      <c r="J37" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="F38">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="G38">
-        <v>2019</v>
+        <v>2011</v>
+      </c>
+      <c r="H38" t="s">
+        <v>191</v>
+      </c>
+      <c r="I38" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -2266,19 +3860,19 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="F39">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="G39">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -2289,19 +3883,19 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="F40">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="G40">
-        <v>2014</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -2312,19 +3906,19 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="F41">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="G41">
-        <v>2013</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -2335,19 +3929,19 @@
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="F42">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="G42">
-        <v>2011</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -2358,19 +3952,19 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="F43">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="G43">
-        <v>2011</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -2381,83 +3975,65 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E44" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="F44">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G44">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" t="s">
-        <v>39</v>
+        <v>59</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F45">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="G45">
-        <v>2019</v>
-      </c>
-      <c r="H45" t="s">
-        <v>10</v>
-      </c>
-      <c r="I45" t="s">
-        <v>10</v>
-      </c>
-      <c r="J45" t="s">
-        <v>10</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" t="s">
-        <v>40</v>
+        <v>61</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F46">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="G46">
-        <v>2019</v>
-      </c>
-      <c r="H46" t="s">
-        <v>10</v>
-      </c>
-      <c r="I46" t="s">
-        <v>10</v>
-      </c>
-      <c r="J46" t="s">
-        <v>10</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -2468,19 +4044,19 @@
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F47">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="G47">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="H47" t="s">
         <v>10</v>
@@ -2499,1554 +4075,20 @@
       <c r="B48" t="s">
         <v>10</v>
       </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="F48">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="G48">
-        <v>2016</v>
-      </c>
-      <c r="H48" t="s">
-        <v>10</v>
-      </c>
-      <c r="I48" t="s">
-        <v>10</v>
-      </c>
-      <c r="J48" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>95</v>
-      </c>
-      <c r="B53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" t="s">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D4E204-A097-E246-8420-89EA1CD35275}">
-  <dimension ref="A1:J54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" customWidth="1"/>
-    <col min="5" max="5" width="24.1640625" customWidth="1"/>
-    <col min="6" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5" customWidth="1"/>
-    <col min="9" max="9" width="11.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2">
-        <v>2009</v>
-      </c>
-      <c r="G2">
-        <v>2015</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3">
-        <v>2007</v>
-      </c>
-      <c r="G3">
-        <v>2009</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4">
-        <v>2003</v>
-      </c>
-      <c r="G4">
-        <v>2007</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F5">
-        <v>2021</v>
-      </c>
-      <c r="G5">
-        <v>9999</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6">
-        <v>2016</v>
-      </c>
-      <c r="G6">
-        <v>2021</v>
-      </c>
-      <c r="H6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7">
-        <v>2015</v>
-      </c>
-      <c r="G7">
-        <v>2016</v>
-      </c>
-      <c r="H7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8">
-        <v>2009</v>
-      </c>
-      <c r="G8">
-        <v>2015</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9">
-        <v>2011</v>
-      </c>
-      <c r="G9">
-        <v>2012</v>
-      </c>
-      <c r="H9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>2024</v>
-      </c>
-      <c r="G10">
-        <v>2024</v>
-      </c>
-      <c r="H10" t="s">
-        <v>170</v>
-      </c>
-      <c r="I10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>2022</v>
-      </c>
-      <c r="G11">
-        <v>2022</v>
-      </c>
-      <c r="H11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>2020</v>
-      </c>
-      <c r="G12">
-        <v>2020</v>
-      </c>
-      <c r="H12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13">
         <v>2019</v>
-      </c>
-      <c r="G13">
-        <v>2019</v>
-      </c>
-      <c r="H13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14">
-        <v>2017</v>
-      </c>
-      <c r="G14">
-        <v>2017</v>
-      </c>
-      <c r="H14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" t="s">
-        <v>182</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15">
-        <v>2024</v>
-      </c>
-      <c r="G15">
-        <v>2024</v>
-      </c>
-      <c r="H15" t="s">
-        <v>183</v>
-      </c>
-      <c r="I15" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16">
-        <v>2024</v>
-      </c>
-      <c r="G16">
-        <v>2024</v>
-      </c>
-      <c r="H16" t="s">
-        <v>180</v>
-      </c>
-      <c r="I16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17">
-        <v>2023</v>
-      </c>
-      <c r="G17">
-        <v>2023</v>
-      </c>
-      <c r="H17" t="s">
-        <v>186</v>
-      </c>
-      <c r="I17" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18">
-        <v>2022</v>
-      </c>
-      <c r="G18">
-        <v>2022</v>
-      </c>
-      <c r="H18" t="s">
-        <v>173</v>
-      </c>
-      <c r="I18" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19">
-        <v>2021</v>
-      </c>
-      <c r="G19">
-        <v>2021</v>
-      </c>
-      <c r="H19" t="s">
-        <v>160</v>
-      </c>
-      <c r="I19" t="s">
-        <v>10</v>
-      </c>
-      <c r="J19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20">
-        <v>2021</v>
-      </c>
-      <c r="G20">
-        <v>2021</v>
-      </c>
-      <c r="H20" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" t="s">
-        <v>10</v>
-      </c>
-      <c r="J20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21">
-        <v>2021</v>
-      </c>
-      <c r="G21">
-        <v>2021</v>
-      </c>
-      <c r="H21" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22">
-        <v>2021</v>
-      </c>
-      <c r="G22">
-        <v>2021</v>
-      </c>
-      <c r="H22" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23">
-        <v>2021</v>
-      </c>
-      <c r="G23">
-        <v>2021</v>
-      </c>
-      <c r="H23" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24">
-        <v>2020</v>
-      </c>
-      <c r="G24">
-        <v>2020</v>
-      </c>
-      <c r="H24" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25">
-        <v>2020</v>
-      </c>
-      <c r="G25">
-        <v>2020</v>
-      </c>
-      <c r="H25" t="s">
-        <v>67</v>
-      </c>
-      <c r="I25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" t="s">
-        <v>154</v>
-      </c>
-      <c r="D26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26">
-        <v>2019</v>
-      </c>
-      <c r="G26">
-        <v>2019</v>
-      </c>
-      <c r="H26" t="s">
-        <v>69</v>
-      </c>
-      <c r="I26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27">
-        <v>2019</v>
-      </c>
-      <c r="G27">
-        <v>2019</v>
-      </c>
-      <c r="H27" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" t="s">
-        <v>10</v>
-      </c>
-      <c r="J27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28">
-        <v>2017</v>
-      </c>
-      <c r="G28">
-        <v>2017</v>
-      </c>
-      <c r="H28" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" t="s">
-        <v>10</v>
-      </c>
-      <c r="J28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29">
-        <v>2017</v>
-      </c>
-      <c r="G29">
-        <v>2017</v>
-      </c>
-      <c r="H29" t="s">
-        <v>120</v>
-      </c>
-      <c r="I29" t="s">
-        <v>10</v>
-      </c>
-      <c r="J29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30">
-        <v>2017</v>
-      </c>
-      <c r="G30">
-        <v>2017</v>
-      </c>
-      <c r="H30" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" t="s">
-        <v>10</v>
-      </c>
-      <c r="J30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31">
-        <v>2016</v>
-      </c>
-      <c r="G31">
-        <v>2016</v>
-      </c>
-      <c r="H31" t="s">
-        <v>80</v>
-      </c>
-      <c r="I31" t="s">
-        <v>10</v>
-      </c>
-      <c r="J31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" t="s">
-        <v>130</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32">
-        <v>2014</v>
-      </c>
-      <c r="G32">
-        <v>2014</v>
-      </c>
-      <c r="H32" t="s">
-        <v>128</v>
-      </c>
-      <c r="I32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33">
-        <v>2013</v>
-      </c>
-      <c r="G33">
-        <v>2013</v>
-      </c>
-      <c r="H33" t="s">
-        <v>123</v>
-      </c>
-      <c r="I33" t="s">
-        <v>10</v>
-      </c>
-      <c r="J33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34">
-        <v>2013</v>
-      </c>
-      <c r="G34">
-        <v>2013</v>
-      </c>
-      <c r="H34" t="s">
-        <v>87</v>
-      </c>
-      <c r="I34" t="s">
-        <v>10</v>
-      </c>
-      <c r="J34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35">
-        <v>2013</v>
-      </c>
-      <c r="G35">
-        <v>2013</v>
-      </c>
-      <c r="H35" t="s">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s">
-        <v>10</v>
-      </c>
-      <c r="J35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36">
-        <v>2012</v>
-      </c>
-      <c r="G36">
-        <v>2012</v>
-      </c>
-      <c r="H36" t="s">
-        <v>125</v>
-      </c>
-      <c r="I36" t="s">
-        <v>10</v>
-      </c>
-      <c r="J36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37">
-        <v>2011</v>
-      </c>
-      <c r="G37">
-        <v>2011</v>
-      </c>
-      <c r="H37" t="s">
-        <v>194</v>
-      </c>
-      <c r="I37" t="s">
-        <v>10</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" t="s">
-        <v>146</v>
-      </c>
-      <c r="F38">
-        <v>2020</v>
-      </c>
-      <c r="G38">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" t="s">
-        <v>147</v>
-      </c>
-      <c r="F39">
-        <v>2019</v>
-      </c>
-      <c r="G39">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40">
-        <v>2018</v>
-      </c>
-      <c r="G40">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" t="s">
-        <v>51</v>
-      </c>
-      <c r="D41" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" t="s">
-        <v>146</v>
-      </c>
-      <c r="F41">
-        <v>2014</v>
-      </c>
-      <c r="G41">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" t="s">
-        <v>146</v>
-      </c>
-      <c r="F42">
-        <v>2013</v>
-      </c>
-      <c r="G42">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E43" t="s">
-        <v>148</v>
-      </c>
-      <c r="F43">
-        <v>2011</v>
-      </c>
-      <c r="G43">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" t="s">
-        <v>59</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F44">
-        <v>2011</v>
-      </c>
-      <c r="G44">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F45">
-        <v>2010</v>
-      </c>
-      <c r="G45">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" t="s">
-        <v>34</v>
-      </c>
-      <c r="E46" t="s">
-        <v>149</v>
-      </c>
-      <c r="F46">
-        <v>2019</v>
-      </c>
-      <c r="G46">
-        <v>2019</v>
-      </c>
-      <c r="H46" t="s">
-        <v>10</v>
-      </c>
-      <c r="I46" t="s">
-        <v>10</v>
-      </c>
-      <c r="J46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" t="s">
-        <v>150</v>
-      </c>
-      <c r="F47">
-        <v>2019</v>
-      </c>
-      <c r="G47">
-        <v>2019</v>
-      </c>
-      <c r="H47" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" t="s">
-        <v>37</v>
-      </c>
-      <c r="E48" t="s">
-        <v>41</v>
-      </c>
-      <c r="F48">
-        <v>2016</v>
-      </c>
-      <c r="G48">
-        <v>2016</v>
       </c>
       <c r="H48" t="s">
         <v>10</v>
@@ -4065,11 +4107,14 @@
       <c r="B49" t="s">
         <v>10</v>
       </c>
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E49" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="F49">
         <v>2016</v>
@@ -4089,57 +4134,86 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>96</v>
+        <v>38</v>
+      </c>
+      <c r="E50" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50">
+        <v>2016</v>
+      </c>
+      <c r="G50">
+        <v>2016</v>
+      </c>
+      <c r="H50" t="s">
+        <v>10</v>
+      </c>
+      <c r="I50" t="s">
+        <v>10</v>
+      </c>
+      <c r="J50" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
         <v>95</v>
-      </c>
-      <c r="B51" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="D52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
